--- a/data/fmsForecastOutput/File1/RPT_RPT4797176857108LO_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4797176857108LO_fmsForecastOutput.xlsx
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>443.4826693607644</v>
+        <v>443.4826696681407</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>484.0977116286941</v>
@@ -1884,13 +1884,13 @@
         <v>527.0813055023985</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>559.7245857367685</v>
+        <v>559.7245857367684</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>597.253810512755</v>
+        <v>597.2538105127549</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>38.25090990715531</v>
+        <v>38.2509099336669</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>44.13434334695889</v>
@@ -1905,7 +1905,7 @@
         <v>66.03487987702341</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>45768259.81775468</v>
+        <v>45768259.84947651</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>53625827.83325036</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>450.9662520398815</v>
+        <v>450.9662523524446</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>492.2666559866926</v>
+        <v>492.2666559866925</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>535.9755798469399</v>
@@ -1937,10 +1937,10 @@
         <v>569.1697016438528</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>607.3322162322669</v>
+        <v>607.3322162322668</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.57938394509963</v>
+        <v>46.57938397738364</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>53.68676849829588</v>
@@ -1955,7 +1955,7 @@
         <v>79.99241380256218</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>45768259.81775468</v>
+        <v>45768259.84947651</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>53625827.83325036</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>506.4552151357395</v>
+        <v>506.4552153988976</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>552.292388722297</v>
+        <v>552.2923887222969</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>601.102965373508</v>
@@ -2182,10 +2182,10 @@
         <v>636.5650044966172</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>677.3085466404946</v>
+        <v>677.3085466404945</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>41.76444147676695</v>
+        <v>41.76444149846809</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>47.89524604244685</v>
@@ -2200,7 +2200,7 @@
         <v>71.10234016957372</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>61049553.28100636</v>
+        <v>61049553.31272819</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>70971545.47112545</v>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>514.9174341425547</v>
+        <v>514.9174344101099</v>
       </c>
       <c r="U10" s="162" t="n">
         <v>561.5242405519014</v>
@@ -2232,10 +2232,10 @@
         <v>647.2089050293806</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>688.6344813880746</v>
+        <v>688.6344813880745</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>48.96904583562141</v>
+        <v>48.96904586106611</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>56.12694363513128</v>
@@ -2247,10 +2247,10 @@
         <v>72.53443251653407</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>83.11345205833511</v>
+        <v>83.1134520583351</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>61049553.28100636</v>
+        <v>61049553.31272819</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>70971545.47112545</v>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>891.394701056047</v>
+        <v>891.3947011348255</v>
       </c>
       <c r="D11" s="156" t="n">
         <v>974.3311947755478</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1061.699815021288</v>
+        <v>1061.699815021289</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1133.431450800131</v>
@@ -2333,34 +2333,34 @@
         <v>1219.361703952043</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>89.27996919275749</v>
+        <v>89.27996920064777</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>101.1247656025734</v>
+        <v>101.1247656025735</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>114.4891849590058</v>
+        <v>114.4891849590059</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>128.8574239897535</v>
+        <v>128.8574239897536</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>146.8939287861138</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>5605932.496101833</v>
+        <v>5605932.496597267</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>6428189.345706714</v>
+        <v>6428189.345706715</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7361192.687222432</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8374037.947878095</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>9674380.582872598</v>
+        <v>9674380.582872599</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1132.02425145797</v>
+        <v>1132.024251558014</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>1237.349223785199</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1348.302763016953</v>
+        <v>1348.302763016954</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1439.398156788308</v>
@@ -2383,7 +2383,7 @@
         <v>1548.525045681235</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>102.2111735361745</v>
+        <v>102.2111735452076</v>
       </c>
       <c r="Z11" s="156" t="n">
         <v>115.8175997626957</v>
@@ -2392,25 +2392,25 @@
         <v>131.1819336447159</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>147.7398256443604</v>
+        <v>147.7398256443605</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>168.5446406658589</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>5605932.496101833</v>
+        <v>5605932.496597267</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>6428189.345706714</v>
+        <v>6428189.345706715</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7361192.687222432</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8374037.947878095</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>9674380.582872598</v>
+        <v>9674380.582872599</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>525.5424118668298</v>
+        <v>525.5424121208454</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>572.9022709483427</v>
@@ -2470,13 +2470,13 @@
         <v>623.3013323322406</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>660.2413178815325</v>
+        <v>660.2413178815323</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>702.7031942079863</v>
+        <v>702.7031942079861</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>43.7214279741694</v>
+        <v>43.72142799530172</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>50.08477099359557</v>
@@ -2491,7 +2491,7 @@
         <v>74.21528525673742</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>66655485.77710818</v>
+        <v>66655485.80932544</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>77399734.81683215</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>539.6595267159731</v>
+        <v>539.6595269768121</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>588.2063942372233</v>
@@ -2523,10 +2523,10 @@
         <v>677.7205504694524</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>721.1908606362679</v>
+        <v>721.1908606362678</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>51.21265003066139</v>
+        <v>51.21265005541451</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>58.63681433110663</v>
@@ -2538,10 +2538,10 @@
         <v>75.68605540325967</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>86.68542807725279</v>
+        <v>86.68542807725281</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>66655485.77710818</v>
+        <v>66655485.80932544</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>77399734.81683215</v>
@@ -2606,46 +2606,46 @@
         <v>2992.005633317737</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3112.054111500075</v>
+        <v>3112.054111500073</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3307.722287153533</v>
+        <v>3307.722287153531</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3469.630894069584</v>
+        <v>3469.630894069582</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3695.3851405864</v>
+        <v>3695.385140586398</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>2655.868210096912</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2759.185740881357</v>
+        <v>2759.185740881356</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>2933.355711025158</v>
+        <v>2933.355711025157</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3074.967999833879</v>
+        <v>3074.967999833878</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3292.912981338575</v>
+        <v>3292.912981338573</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>65207274.24222937</v>
+        <v>65207274.24222936</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>74794356.03350759</v>
+        <v>74794356.03350757</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>88025279.73288214</v>
+        <v>88025279.73288211</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>102424071.6659591</v>
+        <v>102424071.665959</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>122220863.6761782</v>
+        <v>122220863.6761781</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2656,46 +2656,46 @@
         <v>2180.673383629697</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>2268.168713919963</v>
+        <v>2268.168713919962</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>2410.778198982241</v>
+        <v>2410.77819898224</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>2528.782585655433</v>
+        <v>2528.782585655432</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>2693.319801474345</v>
+        <v>2693.319801474343</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>1926.186866041372</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>2001.027514742669</v>
+        <v>2001.027514742668</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>2127.359074101697</v>
+        <v>2127.359074101696</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>2230.005282206311</v>
+        <v>2230.00528220631</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>2388.566174501259</v>
+        <v>2388.566174501257</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>65207274.24222937</v>
+        <v>65207274.24222936</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>74794356.03350759</v>
+        <v>74794356.03350757</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>88025279.73288214</v>
+        <v>88025279.73288211</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>102424071.6659591</v>
+        <v>102424071.665959</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>122220863.6761782</v>
+        <v>122220863.6761781</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>887.2141613875776</v>
+        <v>887.2141616043455</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>956.3842863523615</v>
+        <v>956.3842863523613</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1042.355791489745</v>
+        <v>1042.355791489744</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>1109.580926965817</v>
@@ -2761,10 +2761,10 @@
         <v>1191.670822238224</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>85.12207771440467</v>
+        <v>85.12207773520204</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>96.78590093043991</v>
+        <v>96.78590093043989</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>111.4671416337965</v>
@@ -2776,19 +2776,19 @@
         <v>147.0332174062268</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>131862760.0193376</v>
+        <v>131862760.0515548</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>152194090.8503397</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>177694715.3559531</v>
+        <v>177694715.355953</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>204792952.1891128</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>241225048.3266105</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>859.5093506642763</v>
+        <v>859.5093508742749</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>924.845311304806</v>
+        <v>924.8453113048058</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1005.915160794637</v>
+        <v>1005.915160794636</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>1069.123916450676</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1146.561769738528</v>
+        <v>1146.561769738527</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>98.74428153956389</v>
+        <v>98.7442815636895</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>112.1248011616784</v>
@@ -2823,22 +2823,22 @@
         <v>146.4400814694955</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>169.3999510171</v>
+        <v>169.3999510170999</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>131862760.0193376</v>
+        <v>131862760.0515548</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>152194090.8503397</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>177694715.3559531</v>
+        <v>177694715.355953</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>204792952.1891128</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>241225048.3266105</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>6288.945278068639</v>
+        <v>6288.94527806864</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>6597.540323224021</v>
@@ -3575,10 +3575,10 @@
         <v>6933.403004383898</v>
       </c>
       <c r="F22" s="80" t="n">
-        <v>7388.217383562593</v>
+        <v>7388.217383562594</v>
       </c>
       <c r="G22" s="81" t="n">
-        <v>7933.971151888077</v>
+        <v>7933.971151888078</v>
       </c>
       <c r="H22" s="79" t="n">
         <v>56501.53893456024</v>
@@ -3625,7 +3625,7 @@
         <v>5459.599200665491</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>5817.735633733803</v>
+        <v>5817.735633733804</v>
       </c>
       <c r="X22" s="81" t="n">
         <v>6247.480859191784</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>126831.7918250114</v>
+        <v>126831.7918250115</v>
       </c>
       <c r="D23" s="86" t="n">
         <v>135101.1136484238</v>
@@ -3715,7 +3715,7 @@
         <v>155047.6738590327</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>169351.9904723949</v>
+        <v>169351.990472395</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1397717.813839474</v>
@@ -3896,7 +3896,7 @@
         <v>32975.65810448211</v>
       </c>
       <c r="V24" s="80" t="n">
-        <v>36513.22206665209</v>
+        <v>36513.2220666521</v>
       </c>
       <c r="W24" s="80" t="n">
         <v>40503.3126402252</v>
@@ -3926,7 +3926,7 @@
         <v>37377.97480667131</v>
       </c>
       <c r="AF24" s="80" t="n">
-        <v>41377.72546463594</v>
+        <v>41377.72546463595</v>
       </c>
       <c r="AG24" s="80" t="n">
         <v>45929.96818582567</v>
@@ -4034,7 +4034,7 @@
         <v>1398476.087516877</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>1423997.15512468</v>
+        <v>1423997.155124681</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,19 +4408,19 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>455.9570601309058</v>
+        <v>455.9570601309057</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>509.4239498391404</v>
+        <v>509.4239498391403</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>558.1979235466482</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>600.2901078628598</v>
+        <v>600.2901078628597</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>642.1502042819843</v>
+        <v>642.1502042819842</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>39.32684100990416</v>
@@ -4458,19 +4458,19 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>463.6511428839818</v>
+        <v>463.6511428839817</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>518.0202637668947</v>
+        <v>518.0202637668946</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>567.6172776742717</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>610.4197498173538</v>
+        <v>610.4197498173537</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>652.9862176781401</v>
+        <v>652.98621767814</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>47.889580435982</v>
@@ -4615,7 +4615,7 @@
         <v>520.7513229582903</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>581.2414160333867</v>
+        <v>581.2414160333866</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>636.6507125946796</v>
@@ -4624,7 +4624,7 @@
         <v>682.7643386325049</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>728.2934364777361</v>
+        <v>728.293436477736</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>42.9433590605072</v>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>529.4524116454327</v>
+        <v>529.4524116454326</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>590.9571657696152</v>
+        <v>590.9571657696151</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>647.2950916811642</v>
@@ -4674,7 +4674,7 @@
         <v>694.1807307627464</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>740.4719391402987</v>
+        <v>740.4719391402986</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>50.35133342653079</v>
@@ -4689,7 +4689,7 @@
         <v>77.79869062138901</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>89.36987716651596</v>
+        <v>89.36987716651595</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>62772846.81247865</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>916.6364197805947</v>
+        <v>916.6364197805946</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>1025.500360029521</v>
@@ -4747,13 +4747,13 @@
         <v>5764676.283884914</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>6765779.976775518</v>
+        <v>6765779.976775519</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7797347.65921034</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>8982776.760550832</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>10403905.47481582</v>
@@ -4773,7 +4773,7 @@
         <v>1428.190490294579</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1544.03316446088</v>
+        <v>1544.033164460881</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1665.296094426409</v>
@@ -4788,7 +4788,7 @@
         <v>138.9545399362813</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>158.4795627469387</v>
+        <v>158.4795627469388</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>181.25424100834</v>
@@ -4797,13 +4797,13 @@
         <v>5764676.283884914</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>6765779.976775518</v>
+        <v>6765779.976775519</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7797347.65921034</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>8982776.760550832</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>10403905.47481582</v>
@@ -4825,10 +4825,10 @@
         <v>660.1676208572542</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>708.1653350290728</v>
+        <v>708.1653350290727</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>755.6072362552831</v>
+        <v>755.6072362552829</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>44.9559154006609</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>554.8969727735633</v>
+        <v>554.8969727735632</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>619.0428331718741</v>
@@ -4878,7 +4878,7 @@
         <v>726.9133083328225</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>775.4867738037474</v>
+        <v>775.4867738037473</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>52.65865432351092</v>
@@ -4893,7 +4893,7 @@
         <v>81.17977371312516</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.21166784631458</v>
+        <v>93.2116678463146</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>68537523.09636356</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3077.561852826309</v>
+        <v>3077.561852826308</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3276.191295399594</v>
+        <v>3276.191295399593</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3504.68561893784</v>
+        <v>3504.685618937838</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3722.77992925921</v>
+        <v>3722.779929259209</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>3974.81460749317</v>
+        <v>3974.814607493168</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>2731.81260038769</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2904.711802170078</v>
+        <v>2904.711802170077</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3108.026818208475</v>
+        <v>3108.026818208473</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3299.321888233776</v>
+        <v>3299.321888233775</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3541.909197954797</v>
+        <v>3541.909197954796</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67071872.29194545</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78739189.4236315</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>93266878.29294567</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>109897072.6029603</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>131462690.8423988</v>
@@ -4971,43 +4971,43 @@
         <v>2243.029606695841</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>2387.797361743303</v>
+        <v>2387.797361743302</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>2554.331636980548</v>
+        <v>2554.331636980547</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>2713.28603611098</v>
+        <v>2713.286036110979</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>2896.977306092659</v>
+        <v>2896.977306092657</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>1981.266062581127</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>2106.56649620241</v>
+        <v>2106.566496202409</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>2254.035891186371</v>
+        <v>2254.03589118637</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>2392.709530264282</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>2569.179492848509</v>
+        <v>2569.179492848507</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67071872.29194545</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78739189.4236315</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>93266878.29294567</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>109897072.6029603</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>131462690.8423988</v>
@@ -5047,7 +5047,7 @@
         <v>136.0602585673435</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>158.1273625580411</v>
+        <v>158.127362558041</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>135609395.388309</v>
@@ -5059,7 +5059,7 @@
         <v>188239975.4262301</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>219696460.5068207</v>
+        <v>219696460.5068206</v>
       </c>
       <c r="Q41" s="184" t="n">
         <v>259426280.3175762</v>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>883.9307121820254</v>
+        <v>883.9307121820253</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>973.4743594510561</v>
+        <v>973.4743594510558</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>1065.611010263007</v>
@@ -5082,7 +5082,7 @@
         <v>1146.927849697213</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1233.073667685077</v>
+        <v>1233.073667685076</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>101.549916865607</v>
@@ -5109,7 +5109,7 @@
         <v>188239975.4262301</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>219696460.5068207</v>
+        <v>219696460.5068206</v>
       </c>
       <c r="AH41" s="190" t="n">
         <v>259426280.3175762</v>
@@ -5374,7 +5374,7 @@
         <v>0.181696533592161</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.2015939854953309</v>
+        <v>0.2015939854953308</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.2251057261284327</v>
@@ -5383,7 +5383,7 @@
         <v>0.2491675177064494</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2727982514695381</v>
+        <v>0.272798251469538</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.01567154303209634</v>
@@ -5535,7 +5535,7 @@
         <v>0.04181660358535136</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.04035912649143861</v>
+        <v>0.0403591264914386</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.002647724934822222</v>
@@ -5652,7 +5652,7 @@
         <v>0.02523141550445889</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.02968995016641673</v>
+        <v>0.02968995016641672</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>19450.72208792473</v>
@@ -5680,7 +5680,7 @@
         <v>0.2152038180613243</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.2253608659412577</v>
+        <v>0.2253608659412576</v>
       </c>
       <c r="E49" s="156" t="n">
         <v>0.2371588319298149</v>
@@ -5701,10 +5701,10 @@
         <v>0.02557419808246827</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.0281215971356928</v>
+        <v>0.02812159713569281</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03100599512497865</v>
+        <v>0.03100599512497866</v>
       </c>
       <c r="M49" s="158" t="n">
         <v>1353.405035419108</v>
@@ -5719,7 +5719,7 @@
         <v>1827.533985065208</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>2042.043532149656</v>
+        <v>2042.043532149657</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5742,19 +5742,19 @@
         <v>0.3268587096421819</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.02467620097747285</v>
+        <v>0.02467620097747286</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.02678838028969381</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.0293029665384763</v>
+        <v>0.02930296653847631</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.03224245626700228</v>
+        <v>0.03224245626700229</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.03557597206373389</v>
+        <v>0.0355759720637339</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1353.405035419108</v>
@@ -5769,7 +5769,7 @@
         <v>1827.533985065208</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>2042.043532149656</v>
+        <v>2042.043532149657</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5788,10 +5788,10 @@
         <v>0.2022041730736412</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.2226672927133033</v>
+        <v>0.2226672927133032</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.2426723784433134</v>
+        <v>0.2426723784433133</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.01364608081366838</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.01035805149502585</v>
+        <v>0.01035827059991424</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.00956638207250339</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008933943126142865</v>
+        <v>0.0008934132106725992</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.0008721503548438406</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>1059.714073593138</v>
@@ -6384,22 +6384,22 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01053283923784634</v>
+        <v>0.01053306204003716</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009727810728290083</v>
+        <v>0.009727810728290081</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0.009006054161459897</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003273339381121546</v>
+        <v>0.0003273339381121545</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.001087915471883842</v>
+        <v>0.001087938484667489</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.001060918338086801</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>1059.714073593138</v>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.008867973163611889</v>
+        <v>0.008868160748725868</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0.008246572808612518</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.0007312906159134792</v>
+        <v>0.0007313060849762524</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.000715149514533773</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>1059.714073593138</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009016145655106386</v>
+        <v>0.009016336374527742</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.008384418521908117</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.0008574424180854417</v>
+        <v>0.0008574605556497714</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.0008380613904218283</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>1059.714073593138</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.008428255351927243</v>
+        <v>0.008428433635646835</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.007843858906676755</v>
@@ -6751,13 +6751,13 @@
         <v>0.00729472551885533</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002656841428881557</v>
+        <v>0.0002656841428881556</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0007011714963369502</v>
+        <v>0.0007011863282870061</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.000685732797666643</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>1059.714073593138</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008654655060294099</v>
+        <v>0.008654838133069127</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.00805339444154146</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.0008213101016415642</v>
+        <v>0.0008213274748954282</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.0008028226133383114</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>1059.714073593138</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.007192371584422297</v>
+        <v>0.007192523725370242</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.006659219699978678</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006900584318926571</v>
+        <v>0.0006900730287669611</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.0006739117187029039</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>1059.714073593138</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.006967777228211358</v>
+        <v>0.006967924618292657</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.006439616589648571</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0008004894371372671</v>
+        <v>0.0008005063699695542</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.0007807151324075047</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1068.970728243675</v>
+        <v>1068.993340287284</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>1059.714073593138</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.004396391220535037</v>
+        <v>0.004396484217833629</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>0.006412249531952774</v>
@@ -7312,7 +7312,7 @@
         <v>0.01206934436206961</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.000379193993613524</v>
+        <v>0.0003792020147415993</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>0.0005845935968535278</v>
@@ -7327,7 +7327,7 @@
         <v>0.001334437204275779</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>453.7159838330878</v>
+        <v>453.7255813321974</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>710.3156680238225</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004470578464956654</v>
+        <v>0.004470673031545369</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006520453533702529</v>
+        <v>0.006520453533702528</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.008626234805094212</v>
@@ -7362,7 +7362,7 @@
         <v>0.01227300944901985</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004617569271181174</v>
+        <v>0.0004617666947080962</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.0007111228743822255</v>
@@ -7377,7 +7377,7 @@
         <v>0.001616491969649267</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>453.7159838330878</v>
+        <v>453.7255813321974</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>710.3156680238225</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.00376393951885314</v>
+        <v>0.003764019137838293</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.005527594678058093</v>
@@ -7513,10 +7513,10 @@
         <v>0.008976209188679201</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.01047182351423703</v>
+        <v>0.01047182351423702</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0003103903900270827</v>
+        <v>0.0003103969557457219</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.0004793575152121664</v>
@@ -7531,7 +7531,7 @@
         <v>0.001099308670174259</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>453.7159838330878</v>
+        <v>453.7255813321974</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>710.3156680238225</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.00382683013501237</v>
+        <v>0.003826911084328951</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.005619991271029431</v>
@@ -7566,7 +7566,7 @@
         <v>0.01064693305685051</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.0003639345026229533</v>
+        <v>0.0003639422009655054</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.0005617441074119461</v>
@@ -7578,10 +7578,10 @@
         <v>0.001022808723463221</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001285011692131879</v>
+        <v>0.001285011692131878</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>453.7159838330878</v>
+        <v>453.7255813321974</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>710.3156680238225</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.01198264253573046</v>
+        <v>0.01198272553188943</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01787647302587098</v>
@@ -7618,7 +7618,7 @@
         <v>0.03564412007955492</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001200152923469731</v>
+        <v>0.001200161236167245</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.001855379520059782</v>
@@ -7633,7 +7633,7 @@
         <v>0.004293971853995306</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.35818319386652</v>
+        <v>75.35870515216855</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>117.9407516252103</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01521732396538649</v>
+        <v>0.01521742936613053</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.02270217780276865</v>
@@ -7665,10 +7665,10 @@
         <v>0.03805565241445329</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04526615236116276</v>
+        <v>0.04526615236116275</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001373981642689264</v>
+        <v>0.00137399115938798</v>
       </c>
       <c r="Z71" s="156" t="n">
         <v>0.002124955260778551</v>
@@ -7683,7 +7683,7 @@
         <v>0.004926860824961244</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.35818319386652</v>
+        <v>75.35870515216855</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>117.9407516252103</v>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.004171463316996362</v>
+        <v>0.004171543103438436</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.006130640949447833</v>
@@ -7714,13 +7714,13 @@
         <v>0.008148558258127712</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009976414715730545</v>
+        <v>0.009976414715730544</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.01165112039890257</v>
+        <v>0.01165112039890256</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003470363739304852</v>
+        <v>0.0003470430116006365</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005359583362949179</v>
@@ -7735,7 +7735,7 @@
         <v>0.001230521265724053</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>529.0741670269542</v>
+        <v>529.084286484366</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>828.2564196490328</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004283517121609086</v>
+        <v>0.004283599051273746</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.006294410740017698</v>
@@ -7770,7 +7770,7 @@
         <v>0.01195765383894682</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0004064975274026217</v>
+        <v>0.0004065053023700514</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.0006274739572744082</v>
@@ -7785,7 +7785,7 @@
         <v>0.001437281583011485</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>529.0741670269542</v>
+        <v>529.084286484366</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>828.2564196490328</v>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003559777554647066</v>
+        <v>0.003559845641542259</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.005204744943755705</v>
@@ -7918,13 +7918,13 @@
         <v>0.006876518689355814</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008380766206736076</v>
+        <v>0.008380766206736074</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.0097474698247945</v>
+        <v>0.009747469824794498</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.000341536096739882</v>
+        <v>0.0003415426292077304</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.0005267191605749075</v>
@@ -7939,7 +7939,7 @@
         <v>0.001202682673070548</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>529.0741670269542</v>
+        <v>529.084286484366</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>828.2564196490328</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003448617287306078</v>
+        <v>0.00344868324806913</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.005033106489159095</v>
@@ -7974,7 +7974,7 @@
         <v>0.009378492822202447</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.000396192590664403</v>
+        <v>0.000396200168532116</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.0006101950860585869</v>
@@ -7989,7 +7989,7 @@
         <v>0.001385635093221034</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>529.0741670269542</v>
+        <v>529.084286484366</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>828.2564196490328</v>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>456.1535111072135</v>
+        <v>456.1535114193156</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>509.6415224562401</v>
@@ -8269,13 +8269,13 @@
         <v>558.4403689618165</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>600.5499545928172</v>
+        <v>600.5499545928171</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>642.435071877816</v>
+        <v>642.4350718778159</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>39.34378514124248</v>
+        <v>39.34378516816167</v>
       </c>
       <c r="I79" s="149" t="n">
         <v>46.46312799181871</v>
@@ -8290,7 +8290,7 @@
         <v>71.03030914749181</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>47075914.9240907</v>
+        <v>47075914.95630024</v>
       </c>
       <c r="N79" s="152" t="n">
         <v>56455438.40305563</v>
@@ -8310,22 +8310,22 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>463.8509088875164</v>
+        <v>463.8509092048851</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>518.2415078299861</v>
+        <v>518.2415078299859</v>
       </c>
       <c r="V79" s="149" t="n">
         <v>567.8638142533905</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>610.6839813510968</v>
+        <v>610.6839813510967</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>653.275892294298</v>
+        <v>653.2758922942979</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>47.91021385885063</v>
+        <v>47.910213891631</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>56.51959465202612</v>
@@ -8340,7 +8340,7 @@
         <v>86.04370739269072</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>47075914.9240907</v>
+        <v>47075914.95630024</v>
       </c>
       <c r="AE79" s="152" t="n">
         <v>56455438.40305563</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>520.9253142767368</v>
+        <v>520.9253145439409</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>581.4346859436332</v>
@@ -8476,10 +8476,10 @@
         <v>682.9950257045422</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>728.5458577871523</v>
+        <v>728.5458577871522</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>42.95770712134171</v>
+        <v>42.95770714337649</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>50.42248980708949</v>
@@ -8494,7 +8494,7 @@
         <v>76.48111878471741</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>62793820.22127864</v>
+        <v>62793820.25348818</v>
       </c>
       <c r="N81" s="165" t="n">
         <v>74716434.7989722</v>
@@ -8514,7 +8514,7 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>529.629310136316</v>
+        <v>529.6293104079848</v>
       </c>
       <c r="U81" s="162" t="n">
         <v>591.153666285988</v>
@@ -8526,10 +8526,10 @@
         <v>694.4152751160224</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>740.7285814318559</v>
+        <v>740.7285814318558</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>50.36815660969364</v>
+        <v>50.36815663552954</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>59.08854170698635</v>
@@ -8541,10 +8541,10 @@
         <v>77.82497663419358</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>89.40085212837451</v>
+        <v>89.4008521283745</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>62793820.22127864</v>
+        <v>62793820.25348818</v>
       </c>
       <c r="AE81" s="165" t="n">
         <v>74716434.7989722</v>
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>916.8636062411917</v>
+        <v>916.8636063241878</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>1025.743597368488</v>
@@ -8581,13 +8581,13 @@
         <v>1311.604254483835</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>91.83087404737367</v>
+        <v>91.83087405568635</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>106.4608024544716</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>121.300909132823</v>
+        <v>121.3009091328231</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>138.2560600880815</v>
@@ -8596,16 +8596,16 @@
         <v>158.0061940023745</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>5766105.047103527</v>
+        <v>5766105.047625485</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>6767384.744927467</v>
+        <v>6767384.744927468</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7799159.069755713</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>8984825.692261014</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>10406230.31776842</v>
@@ -8616,13 +8616,13 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1164.36841762085</v>
+        <v>1164.36841772625</v>
       </c>
       <c r="U82" s="156" t="n">
         <v>1302.64026320015</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1428.522274822855</v>
+        <v>1428.522274822856</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>1544.385351607079</v>
@@ -8631,7 +8631,7 @@
         <v>1665.668219288412</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>105.1315484100336</v>
+        <v>105.1315484195503</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>121.9289314107802</v>
@@ -8643,19 +8643,19 @@
         <v>158.5157112353387</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>181.2947438412287</v>
+        <v>181.2947438412288</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>5766105.047103527</v>
+        <v>5766105.047625485</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>6767384.744927467</v>
+        <v>6767384.744927468</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7799159.069755713</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>8984825.692261014</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>10406230.31776842</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>540.55788601468</v>
+        <v>540.5578862727501</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>603.1321085623805</v>
@@ -8677,13 +8677,13 @@
         <v>660.3852683141049</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>708.3982444206447</v>
+        <v>708.3982444206446</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>755.8615597541252</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>44.97060968934483</v>
+        <v>44.97060971081445</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>52.72755069765645</v>
@@ -8695,10 +8695,10 @@
         <v>69.45500450359407</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>79.82955212688479</v>
+        <v>79.82955212688481</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>68559925.26838216</v>
+        <v>68559925.30111367</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>81483819.54389967</v>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>555.078346375571</v>
+        <v>555.0783466405734</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>619.2437712612241</v>
@@ -8733,7 +8733,7 @@
         <v>775.7477883893104</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>52.67586632912666</v>
+        <v>52.67586635427489</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>61.7308522941603</v>
@@ -8745,10 +8745,10 @@
         <v>81.20647303144563</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>93.24304117939313</v>
+        <v>93.24304117939315</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>68559925.26838216</v>
+        <v>68559925.30111367</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>81483819.54389967</v>
@@ -8770,46 +8770,46 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3077.561852826309</v>
+        <v>3077.561852826308</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3276.191295399594</v>
+        <v>3276.191295399593</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3504.68561893784</v>
+        <v>3504.685618937838</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3722.77992925921</v>
+        <v>3722.779929259209</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3974.81460749317</v>
+        <v>3974.814607493168</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>2731.81260038769</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2904.711802170078</v>
+        <v>2904.711802170077</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3108.026818208475</v>
+        <v>3108.026818208473</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3299.321888233776</v>
+        <v>3299.321888233775</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3541.909197954797</v>
+        <v>3541.909197954796</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67071872.29194545</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78739189.4236315</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>93266878.29294567</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>109897072.6029603</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>131462690.8423988</v>
@@ -8823,43 +8823,43 @@
         <v>2243.029606695841</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>2387.797361743303</v>
+        <v>2387.797361743302</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>2554.331636980548</v>
+        <v>2554.331636980547</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>2713.28603611098</v>
+        <v>2713.286036110979</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>2896.977306092659</v>
+        <v>2896.977306092657</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>1981.266062581127</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>2106.56649620241</v>
+        <v>2106.566496202409</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>2254.035891186371</v>
+        <v>2254.03589118637</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>2392.709530264282</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>2569.179492848509</v>
+        <v>2569.179492848507</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>67071872.29194546</v>
+        <v>67071872.29194545</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>78739189.42363153</v>
+        <v>78739189.4236315</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>93266878.2929457</v>
+        <v>93266878.29294567</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>109897072.6029604</v>
+        <v>109897072.6029603</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>131462690.8423988</v>
@@ -8872,43 +8872,43 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>912.5734325015555</v>
+        <v>912.5734327217834</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>1006.837829461618</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1104.397874821074</v>
+        <v>1104.397874821073</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>1190.524717508094</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1281.79911833712</v>
+        <v>1281.799118337119</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>87.5551248190278</v>
+        <v>87.55512484015715</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>101.891789530499</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>118.1017799659395</v>
+        <v>118.1017799659394</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>136.0826231340085</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>158.1536150088733</v>
+        <v>158.1536150088732</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>135631797.5603276</v>
+        <v>135631797.5930591</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>160223008.9675312</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>188271286.6453921</v>
+        <v>188271286.645392</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>219732572.5662038</v>
@@ -8922,43 +8922,43 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>884.0767342759235</v>
+        <v>884.0767344892741</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>973.6350326011251</v>
+        <v>973.6350326011249</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1065.788260498024</v>
+        <v>1065.788260498023</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1147.116373110476</v>
+        <v>1147.116373110475</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1233.278383714673</v>
+        <v>1233.278383714672</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>101.566692537378</v>
+        <v>101.5666925618887</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>118.0398852651653</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>136.6136799596382</v>
+        <v>136.6136799596381</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>157.1228671892125</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>182.2119865721296</v>
+        <v>182.2119865721295</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>135631797.5603276</v>
+        <v>135631797.5930591</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>160223008.9675312</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>188271286.6453921</v>
+        <v>188271286.645392</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>219732572.5662038</v>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>6288.945278068639</v>
+        <v>6288.94527806864</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>6597.540323224021</v>
@@ -9645,10 +9645,10 @@
         <v>6933.403004383898</v>
       </c>
       <c r="F93" s="80" t="n">
-        <v>7388.217383562593</v>
+        <v>7388.217383562594</v>
       </c>
       <c r="G93" s="81" t="n">
-        <v>7933.971151888077</v>
+        <v>7933.971151888078</v>
       </c>
       <c r="H93" s="79" t="n">
         <v>56501.53893456024</v>
@@ -9695,7 +9695,7 @@
         <v>5459.599200665491</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>5817.735633733803</v>
+        <v>5817.735633733804</v>
       </c>
       <c r="X93" s="81" t="n">
         <v>6247.480859191784</v>
@@ -9756,7 +9756,7 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>126831.7918250114</v>
+        <v>126831.7918250115</v>
       </c>
       <c r="D94" s="86" t="n">
         <v>135101.1136484238</v>
@@ -9768,7 +9768,7 @@
         <v>155047.6738590327</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>169351.9904723949</v>
+        <v>169351.990472395</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1397717.813839474</v>
@@ -9924,7 +9924,7 @@
         <v>32975.65810448211</v>
       </c>
       <c r="V95" s="80" t="n">
-        <v>36513.22206665209</v>
+        <v>36513.2220666521</v>
       </c>
       <c r="W95" s="80" t="n">
         <v>40503.3126402252</v>
@@ -9954,7 +9954,7 @@
         <v>37377.97480667131</v>
       </c>
       <c r="AF95" s="80" t="n">
-        <v>41377.72546463594</v>
+        <v>41377.72546463595</v>
       </c>
       <c r="AG95" s="80" t="n">
         <v>45929.96818582567</v>
@@ -10080,7 +10080,7 @@
         <v>1398476.087516877</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>1423997.15512468</v>
+        <v>1423997.155124681</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
